--- a/wolf/Excel/Tab2_二级页签.xlsx
+++ b/wolf/Excel/Tab2_二级页签.xlsx
@@ -167,7 +167,7 @@
     <t>Text_Tab2_115</t>
   </si>
   <si>
-    <t>1020|1015|1014|1018|1016|1017|1019|1021</t>
+    <t>1020|1015|1048|1014|1018|1016|1017|1019|1021</t>
   </si>
   <si>
     <r>
